--- a/www/download/COUNTRY.DEU.zdW16.xlsx
+++ b/www/download/COUNTRY.DEU.zdW16.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>Alemanha</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Zero depreciation</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,1848 +852,3409 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.467</t>
+          <t>1.0827197921178</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.463</t>
+          <t>1.11656989727557</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.496</t>
+          <t>1.0575296108291</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.592</t>
+          <t>0.884016973125884</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.663</t>
+          <t>0.803923144947343</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.684</t>
+          <t>0.803793907242183</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.709</t>
+          <t>0.796431984708506</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.817</t>
+          <t>0.729660707770887</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.67990209409845</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.71694866647548</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0.839</t>
+          <t>0.75431847325941</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0.901</t>
+          <t>0.718390804597701</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>0.856</t>
+          <t>0.778331257783312</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>0.908</t>
+          <t>0.75295534974776</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.752707484413446</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>39.917</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>39.809</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>39.63</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>39.2</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>39.337</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>39.326</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>39.635</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>40.325</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>40.856</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>40.892</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>41.02</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>41.577</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>42.06</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>42.328</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>42.706</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>35.922</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>35.797</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>35.57</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>35.078</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>35.079</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>34.916</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>35.152</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>35.798</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>36.353</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>36.407</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>36.533</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>37.014</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>37.5</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>37.869</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>38.307</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>54230.834</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>53816.067</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>53261.028</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>52441.828</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>52425.683</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>52007.014</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>53236.784</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>54300.962</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>54743.133</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>52783.931</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>53743.088</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>54658.328</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>54707.034</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>54610.75</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>55404.125</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>48833</t>
+          <t>64242032276.6378</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>48420</t>
+          <t>61439444073.7433</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>47834</t>
+          <t>59100938673.3654</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>46977</t>
+          <t>61742519629.4127</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>46814</t>
+          <t>62963004569.6934</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>46211</t>
+          <t>62664041829.6961</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>47231</t>
+          <t>66482677979.3315</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>48198</t>
+          <t>68989911964.4131</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>48697</t>
+          <t>68709306466.1903</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>46937</t>
+          <t>61572500523.4215</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>47843</t>
+          <t>64800215364.6215</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>48666</t>
+          <t>71090555420.6706</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>48785</t>
+          <t>67514343383.9202</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>48868</t>
+          <t>68224280389.7992</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>49721</t>
+          <t>67181714981.7987</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>33888671811.6766</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>32700968045.6508</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>32657521225.7938</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>36011331197.9148</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>37077879069.2573</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>35676640949.1646</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>36458734745.8814</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>37052910842.9012</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>35728406125.8678</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>34102984436.2156</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>31185556906.5971</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>34007867604.7436</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>31613827340.7188</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>35061775959.3565</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>35588071454.5175</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>1166929.46137771</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1134830.56100238</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>1067153.75293221</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>971237.936466916</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>869344.143040129</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>856168.520312878</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>783342.060204887</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>684494.121595367</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>618997.077976265</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>672403.291516057</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>667558.890419091</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>613197.991374627</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>614919.416997523</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>604897.893252394</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>585754.632488211</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>247361.574695648</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>239446.670663212</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>237798.002828505</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>253914.794053069</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>278496.600497315</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>295148.413767936</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>316548.941107843</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>360314.301079474</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>397185.324811847</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>347083.139567625</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>393251.407974302</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>429784.538602638</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>421920.187512168</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>420171.73828394</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>429135.165117188</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>582761.303531784</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>549177.127272767</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>532160.210762653</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>605258.316092798</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>680191.946314986</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>731175.647720332</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>819725.41198056</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>954220.151200086</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>1036498.5895378</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>848860.909825268</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>987007.239057392</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>1154526.24276837</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>1071026.63820939</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>1076013.3701997</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>1063269.33224329</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>0.440983000790671</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>0.48069011083725</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>0.464716188019174</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0.304506066210631</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>0.262585702719315</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>0.295273287242645</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>0.29546459385389</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>0.300788491472431</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>0.362977117659409</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>0.376331156230283</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>0.534139670594727</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>0.431021802531713</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>0.543153869799391</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>0.39376853176655</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>0.397125440290991</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1.0827197921178</t>
+          <t>943.396019477663</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.11656989727557</t>
+          <t>913.51141284607</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.0575296108291</t>
+          <t>918.119798307389</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0.884016973125884</t>
+          <t>1026.60730936527</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0.803923144947343</t>
+          <t>1056.9822135539</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>0.803793907242183</t>
+          <t>1021.784882265</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>0.796431984708506</t>
+          <t>1037.1738377868</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>0.729660707770887</t>
+          <t>1035.05533389858</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>0.67990209409845</t>
+          <t>982.818642914416</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>0.71694866647548</t>
+          <t>936.715039311551</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>0.75431847325941</t>
+          <t>853.627046960204</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>0.718390804597701</t>
+          <t>918.783908919425</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>0.778331257783312</t>
+          <t>843.035395752501</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>0.75295534974776</t>
+          <t>925.870130168647</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>0.752707484413446</t>
+          <t>929.022670909168</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>1.035</t>
+          <t>40377988296.3733</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.019</t>
+          <t>43272501031.9057</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1.082</t>
+          <t>50368161302.8468</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>1.297</t>
+          <t>57259767956.9671</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>1.429</t>
+          <t>64663660687.1078</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>1.426</t>
+          <t>62515250125.6041</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>1.463</t>
+          <t>64767739557.6483</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>1.641</t>
+          <t>68710827447.9899</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>1.826</t>
+          <t>63956729031.2612</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>1.737</t>
+          <t>57513437852.0293</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1.699</t>
+          <t>53776576334.0222</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>1.861</t>
+          <t>58169351031.4613</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>1.785</t>
+          <t>54497308655.7725</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>1.897</t>
+          <t>59146503606.2021</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>61059435341.8522</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>1.134</t>
+          <t>41411097261.224</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.118</t>
+          <t>44327388322.8893</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>49521471137.2321</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>1.429</t>
+          <t>56569638411.7758</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>62133294176.2439</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>1.584</t>
+          <t>60207298987.0397</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>1.628</t>
+          <t>61845314444.5583</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>1.825</t>
+          <t>65744849977.1437</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>2.027</t>
+          <t>60608391419.2794</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>1.929</t>
+          <t>54379025532.3813</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1.887</t>
+          <t>53260859626.8508</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>2.068</t>
+          <t>58561017684.6572</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>54486917621.6967</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>2.098</t>
+          <t>60660551985.6021</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2.174</t>
+          <t>62313058053.3893</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>6.265</t>
+          <t>-1033108964.85076</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>6.172</t>
+          <t>-1054887290.98361</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>6.567</t>
+          <t>846690165.614742</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>7.909</t>
+          <t>690129545.191318</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>8.851</t>
+          <t>2530366510.86389</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>8.982</t>
+          <t>2307951138.56431</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>9.319</t>
+          <t>2922425113.09003</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>10.777</t>
+          <t>2965977470.84615</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>12.019</t>
+          <t>3348337611.98182</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>11.559</t>
+          <t>3134412319.64803</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>11.175</t>
+          <t>515716707.171343</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>12.145</t>
+          <t>-391666653.195925</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>11.577</t>
+          <t>10391034.0757701</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>12.309</t>
+          <t>-1514048379.4</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>12.646</t>
+          <t>-1253622711.53708</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>3.462</t>
+          <t>1359.4176270809</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>1352.62731513814</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>3.636</t>
+          <t>1344.78493112173</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>4.422</t>
+          <t>1339.21546268316</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>5.025</t>
+          <t>1334.53063086177</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>5.185</t>
+          <t>1323.49066330622</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>5.525</t>
+          <t>1343.62198452435</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>6.376</t>
+          <t>1346.38806637242</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>7.076</t>
+          <t>1339.55932110142</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>6.239</t>
+          <t>1289.23009311396</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>6.332</t>
+          <t>1309.58311663428</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>7.116</t>
+          <t>1314.79980547901</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>6.609</t>
+          <t>1300.93333333333</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>6.915</t>
+          <t>1290.44865193166</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>7.067</t>
+          <t>1297.96120813428</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>1.763</t>
+          <t>1358.58993324499</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.764</t>
+          <t>1351.85678580254</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>1343.9573161277</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2.268</t>
+          <t>1337.8017342922</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2.559</t>
+          <t>1332.73211125134</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2.59</t>
+          <t>1322.45877334696</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>2.718</t>
+          <t>1343.17607634152</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>3.099</t>
+          <t>1346.58305979153</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>1339.90436614418</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>3.079</t>
+          <t>1290.81313624687</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>3.078</t>
+          <t>1310.16791095727</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>3.38</t>
+          <t>1314.62895724344</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>3.18</t>
+          <t>1300.69029006676</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>3.369</t>
+          <t>1290.18026934914</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>3.485</t>
+          <t>1297.33818908316</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>585631.903815757</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>603253.79481513</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>656703.022958823</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>796516.221929919</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>966627.39203301</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>1041569.4269905</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>1184646.84820391</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>1450072.55563788</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>1597629.49088081</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>1251865.66878128</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>1385308.52206712</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>1620051.62711112</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>1547390.56962973</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>1623267.18203129</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>1682252.86969808</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>15181954561.4301</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>15372038746.8088</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>15293348493.3401</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>16162416873.556</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>17423945391.2308</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>18182960319.218</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>20230796184.7702</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>22083532352.7492</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>22075062669.4714</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>18470706589.0803</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>20770413260.8862</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>23703784273.9125</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>22693779202.3505</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>23413117162.0161</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>23275147049.0724</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>521065.392292418</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>510575.637380091</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>504431.005945879</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>627107.305827647</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>739956.879965173</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>805558.506785831</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>925930.950445569</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>1105569.31618612</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>1239346.11926642</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>970364.726826481</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>1094682.27764425</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>1309010.70487049</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>1208666.93514312</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>1274550.356326</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>1291851.97771858</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>54230.834</t>
+          <t>46730156691.6666</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>53816.067</t>
+          <t>45453576557.0416</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>53261.028</t>
+          <t>43851811498.7784</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>52441.828</t>
+          <t>50550326573.4456</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>52425.683</t>
+          <t>54201729726.9894</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>52007.014</t>
+          <t>54364308263.4278</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>53236.784</t>
+          <t>58799970303.5803</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>54300.962</t>
+          <t>60880648031.0037</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>54743.133</t>
+          <t>58870759008.7086</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>52783.931</t>
+          <t>52013857595.0052</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>53743.088</t>
+          <t>52486276828.5461</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>54658.328</t>
+          <t>59521493705.0697</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>54707.034</t>
+          <t>52687992344.7681</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>54610.75</t>
+          <t>57082105942.7397</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>55404.125</t>
+          <t>56085537172.6348</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>48833</t>
+          <t>64566.5115233397</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>48420</t>
+          <t>92678.1574350387</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>47834</t>
+          <t>152272.017012944</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>46977</t>
+          <t>169408.916102271</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>46814</t>
+          <t>226670.512067837</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>46211</t>
+          <t>236010.920204669</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>47231</t>
+          <t>258715.897758345</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>48198</t>
+          <t>344503.239451758</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>48697</t>
+          <t>358283.371614397</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>46937</t>
+          <t>281500.941954798</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>47843</t>
+          <t>290626.244422868</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>48666</t>
+          <t>311040.922240633</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>48785</t>
+          <t>338723.634486615</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>48868</t>
+          <t>348716.825705287</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>49721</t>
+          <t>390400.891979504</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>78178.645</t>
+          <t>-31548202130.2365</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>74981.878</t>
+          <t>-30081537810.2327</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>72665.697</t>
+          <t>-28558463005.4383</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>76973.109</t>
+          <t>-34387909699.8896</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>78675.209</t>
+          <t>-36777784335.7586</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>78710.999</t>
+          <t>-36181347944.2099</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>83553.979</t>
+          <t>-38569174118.8101</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>85665.267</t>
+          <t>-38797115678.2545</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>86164.424</t>
+          <t>-36795696339.2373</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>77612.887</t>
+          <t>-33543151005.9249</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>80052.037</t>
+          <t>-31715863567.6598</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>87533.564</t>
+          <t>-35817709431.1572</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>82967.802</t>
+          <t>-29994213142.4176</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>83806.494</t>
+          <t>-33668988780.7237</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>67181.715</t>
+          <t>-32810390123.5624</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.635</t>
+          <t>789953.2328</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.603</t>
+          <t>778682.1068</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.588</t>
+          <t>821183.6256</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.678</t>
+          <t>982746.968</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.766</t>
+          <t>1115206.106</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.823</t>
+          <t>1125334.4817</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.923</t>
+          <t>1193976.4076</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>1.069</t>
+          <t>1367839.8595</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>1.167</t>
+          <t>1489407.0908</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.956</t>
+          <t>1311255.6644</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1.093</t>
+          <t>1379384.2215</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>1.269</t>
+          <t>1528372.848</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>1.172</t>
+          <t>1452104.0864</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>1.183</t>
+          <t>1531708.3548</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>1.063</t>
+          <t>1585150.47557349</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>27268.472</t>
+          <t>0.100410799800556</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>26788.207</t>
+          <t>0.104734089618353</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>26409.5</t>
+          <t>0.106576012045299</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>25901.898</t>
+          <t>0.10608827389988</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>25779.462</t>
+          <t>0.110686863048172</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>25295.143</t>
+          <t>0.112046106795794</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>25673.257</t>
+          <t>0.11702836140327</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>26050.647</t>
+          <t>0.118222076293376</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>26329.344</t>
+          <t>0.113408880839821</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>25175.829</t>
+          <t>0.0994740277283884</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>25818.226</t>
+          <t>0.106608984483301</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>26464.207</t>
+          <t>0.108040835132793</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>26596.598</t>
+          <t>0.1036188529275</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>26640.853</t>
+          <t>0.103313640980579</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>27114.519</t>
+          <t>0.103673717660963</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.222</t>
+          <t>1034917.8136</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.216</t>
+          <t>1018950.0924</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.214</t>
+          <t>1082483.1648</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.228</t>
+          <t>1296600.6704</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.251</t>
+          <t>1428522.1258</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.265</t>
+          <t>1425585.5757</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.284</t>
+          <t>1463134.3572</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.325</t>
+          <t>1640584.435</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.357</t>
+          <t>1825664.3284</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>1737450.7524</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>0.352</t>
+          <t>1699498.3491</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>0.384</t>
+          <t>1861484.016</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>0.376</t>
+          <t>1784833.8816</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>0.376</t>
+          <t>1896981.0102</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>0.429</t>
+          <t>1969899.23686706</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>39294.519</t>
+          <t>1134332.2704</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>37790.813</t>
+          <t>1117823.4368</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>37876.852</t>
+          <t>1189784.1792</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>41829.607</t>
+          <t>1429100.3888</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>42897.648</t>
+          <t>1579817.6828</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>41469.927</t>
+          <t>1583912.2299</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>42414.751</t>
+          <t>1627708.3604</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>42665.415</t>
+          <t>1825074.2925</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>41554.235</t>
+          <t>2026672.6812</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>39866.455</t>
+          <t>1928817.3124</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>36193.966</t>
+          <t>1886562.5733</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>39413.315</t>
+          <t>2067731.088</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>36816.269</t>
+          <t>1980457.5296</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>40453.716</t>
+          <t>2097501.5325</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>35588.071</t>
+          <t>2173765.66058179</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>24.27</t>
+          <t>6264655.0376</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>28.13</t>
+          <t>6172258.4648</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>26.29</t>
+          <t>6566673.8112</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>12.31</t>
+          <t>7908772.3568</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>9.13</t>
+          <t>8850763.9626</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>11.43</t>
+          <t>8982103.416</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>11.36</t>
+          <t>9319358.266</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>12.97</t>
+          <t>10777340.641</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>17.19</t>
+          <t>12018711.3276</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>17.74</t>
+          <t>11559152.5412</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>32.19</t>
+          <t>11174559.9489</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>23.48</t>
+          <t>12144977.28</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>32.51</t>
+          <t>11576806.032</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>20.8</t>
+          <t>12309141.5754</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>39.71</t>
+          <t>12645545.6859586</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>1.467</t>
+          <t>1316785.76634243</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1.429</t>
+          <t>1325075.75425561</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1306166.79355357</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>1.238</t>
+          <t>1279751.49736786</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>1.105</t>
+          <t>1259269.54036351</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1252847.18375193</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>1.011</t>
+          <t>1275267.21178081</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>0.871</t>
+          <t>1298061.94368916</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>0.795</t>
+          <t>1331673.09591225</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>0.872</t>
+          <t>1292323.77405901</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>0.852</t>
+          <t>1314346.5284</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>1358094.75571983</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>0.784</t>
+          <t>1384658.59982404</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>0.768</t>
+          <t>1382369.6310969</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>0.586</t>
+          <t>1400792.68845859</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>1206343.41028535</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1213954.98691728</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>1191721.01332287</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>1162563.5245853</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>1139752.89315389</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>1128474.93528646</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>1148242.42476639</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>1169196.41769414</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>1201600.40072695</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>1161308.941406</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>1184021.0268</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>1224910.26727619</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>1250618.2346577</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>1255468.76314651</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>1275411.14600798</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>629039.0228</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>646445.8712</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>699849.9072</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>839028.008</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>979663.2986</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>1006409.7186</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>1090629.2272</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>1274119.5875</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>1363028.6008</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>1149835.4604</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>1191308.4882</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>1312153.488</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>1199575.3616</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>1271702.2335</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>1311010.73311488</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>4.8833e+10</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>4.842e+10</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>4.7834e+10</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>4.6977e+10</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>4.6814e+10</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>4.6211e+10</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>4.7231e+10</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>4.8198e+10</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>4.8697e+10</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>4.6937e+10</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>4.7843e+10</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>4.8666e+10</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>4.8785e+10</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>4.8868e+10</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>4.9721e+10</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>54230834365.3405</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>53816066786.0133</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>53261028438.1409</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>52441827984.2541</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>52425683060.2941</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>52007013720.6426</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>53236783785.796</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>54300961886.0936</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>54743132783.1866</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>52783930767.4069</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>53743087707.4673</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>54658328155.3105</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>54707033600.2079</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>54610750441.0103</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>55404124702.9855</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>27268471961.4899</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>26788206573.5587</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>26409500179.7955</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>25901897981.7143</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>25779462436.6757</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>25295142971.4418</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>25673257177.0877</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>26050646572.2076</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>26329344276.8118</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>25175828625.5605</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>25818225967.1286</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>26464207073.5573</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>26596597511.2707</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>26640853430.3182</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>27114518849.8424</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>39917000</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>39809000</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>39630000</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>39200000</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>39337000</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>39326000</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>39635000</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>40325000</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>40856000</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>40892000</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>41020000</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>41577000</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>42060000</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>42328000</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>42706000</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>35922000</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>35797000</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>35570000</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>35078000</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>35079000</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>34916000</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>35152000</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>35798000</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>36353000</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>36407000</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>36533000</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>37014000</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>37500000</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>37869000</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>38307000</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>54230834365.3405</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>53816066786.0133</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>53261028438.1409</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>52441827984.2541</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>52425683060.2941</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>52007013720.6426</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>53236783785.796</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>54300961886.0936</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>54743132783.1866</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>52783930767.4069</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>53743087707.4673</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>54658328155.3105</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>54707033600.2079</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>54610750441.0103</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>55404124702.9855</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>4.8833e+10</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>4.842e+10</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>4.7834e+10</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>4.6977e+10</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>4.6814e+10</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>4.6211e+10</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>4.7231e+10</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>4.8198e+10</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>4.8697e+10</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>4.6937e+10</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>4.7843e+10</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>4.8666e+10</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>4.8785e+10</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>4.8868e+10</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>4.9721e+10</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>3461853.2212</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>3460336.8848</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>3636377.6112</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>4422279.344</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>5025494.0729</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>5185113.9483</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>5525497.5748</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>6375749.647</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>7076454.1568</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>6239144.0408</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>6331706.2611</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>7115837.184</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>6608792.784</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>6914995.6923</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>7066740.533</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>1763371.2932</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1764269.308</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>1889634.0864</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>2268128.3968</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>2559480.9814</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>2590323.1926</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>2718338.8432</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>3099193.88</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>3389701.282</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>3078652.7728</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>3077871.0615</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>3379884.576</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>3180034.176</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>3369203.766</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>3484775.065</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>6949965.55864037</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>6978103.96596191</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>6961474.91279401</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>6982657.7163007</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>7038511.3855933</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>7099367.81342859</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>7185000.6978401</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>7496930.56371886</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>7665061.56581095</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>7765504.37608327</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>7785187.8772</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>7893681.04751317</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>8038793.47694366</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>8152738.97832041</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>8222196.70787723</t>
         </is>
       </c>
     </row>
@@ -2699,7 +4265,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2722,36 +4288,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -2763,331 +4344,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3124,6 +5069,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Zero depreciation</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>zdW16</t>
